--- a/outputs/38985.xlsx
+++ b/outputs/38985.xlsx
@@ -234,92 +234,96 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -575,184 +579,184 @@
   <dimension ref="C4:N13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="4" style="0" width="14.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="4" style="1" width="14.14"/>
   </cols>
   <sheetData>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="L4" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="F6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="G6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="H6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="L6" s="2" t="s">
+      <c r="L6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M6" s="3" t="s">
+      <c r="M6" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="N6" s="4" t="s">
+      <c r="N6" s="5" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="G7" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="I7" s="8"/>
-      <c r="L7" s="5" t="s">
+      <c r="I7" s="9"/>
+      <c r="L7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="M7" s="6" t="s">
+      <c r="M7" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="N7" s="9" t="s">
+      <c r="N7" s="10" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="10" t="str">
-        <f aca="false">INDEX($M$7:$M$11,MATCH(C8,$L$7:$L$11,0))</f>
+      <c r="D8" s="11" t="str">
+        <f aca="false">VLOOKUP(C8,$L$7:$N$11,2,FALSE())</f>
         <v>Blue</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="I8" s="8"/>
-      <c r="L8" s="5" t="s">
+      <c r="I8" s="9"/>
+      <c r="L8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="M8" s="7" t="s">
+      <c r="M8" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="N8" s="11" t="s">
+      <c r="N8" s="12" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="12" t="str">
-        <f aca="false">INDEX($M$7:$M$11,MATCH(C9,$L$7:$L$11,0))</f>
+      <c r="D9" s="13" t="str">
+        <f aca="false">VLOOKUP(C9,$L$7:$N$11,2,FALSE())</f>
         <v>Red</v>
       </c>
-      <c r="E9" s="12"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
-      <c r="I9" s="8"/>
-      <c r="L9" s="5" t="s">
+      <c r="E9" s="13"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="14"/>
+      <c r="I9" s="9"/>
+      <c r="L9" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="M9" s="10" t="s">
+      <c r="M9" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="N9" s="14" t="s">
+      <c r="N9" s="15" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="6" t="str">
-        <f aca="false">INDEX($M$7:$M$11,MATCH(C10,$L$7:$L$11,0))</f>
+      <c r="D10" s="7" t="str">
+        <f aca="false">VLOOKUP(C10,$L$7:$N$11,2,FALSE())</f>
         <v>Red</v>
       </c>
-      <c r="E10" s="6"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="I10" s="8"/>
-      <c r="L10" s="5" t="s">
+      <c r="E10" s="7"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="I10" s="9"/>
+      <c r="L10" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="M10" s="12" t="s">
+      <c r="M10" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="N10" s="15" t="s">
+      <c r="N10" s="16" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C11" s="16" t="s">
+      <c r="C11" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="17" t="str">
-        <f aca="false">INDEX($M$7:$M$11,MATCH(C11,$L$7:$L$11,0))</f>
+      <c r="D11" s="18" t="str">
+        <f aca="false">VLOOKUP(C11,$L$7:$N$11,2,FALSE())</f>
         <v>Red</v>
       </c>
-      <c r="E11" s="17"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="19"/>
-      <c r="I11" s="20"/>
-      <c r="L11" s="16" t="s">
+      <c r="E11" s="18"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="20"/>
+      <c r="I11" s="21"/>
+      <c r="L11" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="M11" s="18" t="s">
+      <c r="M11" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="N11" s="21" t="s">
+      <c r="N11" s="22" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L12" s="0" t="s">
+      <c r="L12" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="M12" s="0" t="s">
+      <c r="M12" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="N12" s="0" t="s">
+      <c r="N12" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L13" s="0" t="s">
+      <c r="L13" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="M13" s="0" t="s">
+      <c r="M13" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="N13" s="0" t="s">
+      <c r="N13" s="1" t="s">
         <v>16</v>
       </c>
     </row>

--- a/outputs/38985.xlsx
+++ b/outputs/38985.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="17">
   <si>
     <t xml:space="preserve">Table 1:</t>
   </si>
@@ -279,7 +279,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -653,9 +653,8 @@
       <c r="C8" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="11" t="str">
-        <f aca="false">VLOOKUP(C8,$L$7:$N$11,2,FALSE())</f>
-        <v>Blue</v>
+      <c r="D8" s="11" t="s">
+        <v>12</v>
       </c>
       <c r="E8" s="11" t="s">
         <v>12</v>
@@ -668,17 +667,14 @@
         <v>12</v>
       </c>
       <c r="N8" s="12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C9" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="13" t="str">
-        <f aca="false">VLOOKUP(C9,$L$7:$N$11,2,FALSE())</f>
-        <v>Red</v>
-      </c>
+      <c r="D9" s="13"/>
       <c r="E9" s="13"/>
       <c r="F9" s="14"/>
       <c r="G9" s="14"/>
@@ -687,20 +683,17 @@
         <v>14</v>
       </c>
       <c r="M9" s="11" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N9" s="15" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="7" t="str">
-        <f aca="false">VLOOKUP(C10,$L$7:$N$11,2,FALSE())</f>
-        <v>Red</v>
-      </c>
+      <c r="D10" s="7"/>
       <c r="E10" s="7"/>
       <c r="F10" s="8"/>
       <c r="G10" s="8"/>
@@ -712,17 +705,14 @@
         <v>10</v>
       </c>
       <c r="N10" s="16" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C11" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="18" t="str">
-        <f aca="false">VLOOKUP(C11,$L$7:$N$11,2,FALSE())</f>
-        <v>Red</v>
-      </c>
+      <c r="D11" s="18"/>
       <c r="E11" s="18"/>
       <c r="F11" s="19"/>
       <c r="G11" s="19"/>
@@ -732,10 +722,10 @@
         <v>15</v>
       </c>
       <c r="M11" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="N11" s="22" t="s">
         <v>11</v>
-      </c>
-      <c r="N11" s="22" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
